--- a/parent_codes.xlsx
+++ b/parent_codes.xlsx
@@ -190,12 +190,12 @@
     <t>FRAGRA1055</t>
   </si>
   <si>
+    <t>GANFAR1121</t>
+  </si>
+  <si>
     <t>GANJOS1056</t>
   </si>
   <si>
-    <t>GANOLU1057</t>
-  </si>
-  <si>
     <t>HAMZAI1058</t>
   </si>
   <si>
@@ -547,10 +547,10 @@
     <t>FRANKLIN GRACE-ANN ITSHOGHENE</t>
   </si>
   <si>
+    <t>GANIYU FARHAN OLUWAJEDALO</t>
+  </si>
+  <si>
     <t>GANFO JOSHUA OLAMIDE</t>
-  </si>
-  <si>
-    <t>GANIYU OLUWAJUEDALO FARHAN</t>
   </si>
   <si>
     <t>HAMMED ZAINAB ENIOLA</t>
